--- a/4_Validaciones/Informe Ventas y Egresos/Asiento contable (account.move)_Egresos.xlsx
+++ b/4_Validaciones/Informe Ventas y Egresos/Asiento contable (account.move)_Egresos.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOPORTE\Desktop\vaope-bi\4_Validaciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOPORTE\Desktop\vaope-bi\4_Validaciones\Informe Ventas y Egresos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E713252-90DD-4194-A5C9-2E3BC6D4005C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E582FE35-822A-4062-B667-2F6EE055F6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-1485" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Costos" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Checklist" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Costos!$A$1:$W$723</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4458" uniqueCount="980">
   <si>
     <t>Número</t>
   </si>
@@ -2841,6 +2841,539 @@
   </si>
   <si>
     <t>Q</t>
+  </si>
+  <si>
+    <t>Tipo de Validación</t>
+  </si>
+  <si>
+    <t>Detalle / Reglas</t>
+  </si>
+  <si>
+    <t>Frecuencia</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Excel Odoo – Ventas</t>
+  </si>
+  <si>
+    <t>Estructura</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verificar columnas: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VentaID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ClienteID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProductoID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Fecha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Cantidad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Precio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Descuento</t>
+    </r>
+  </si>
+  <si>
+    <t>Cada descarga</t>
+  </si>
+  <si>
+    <t>BI Developer</t>
+  </si>
+  <si>
+    <t>Integridad</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Todas las ventas deben tener </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProductoID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ClienteID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> válidos</t>
+    </r>
+  </si>
+  <si>
+    <t>Duplicados</t>
+  </si>
+  <si>
+    <t>No debe haber FacturaID repetidos</t>
+  </si>
+  <si>
+    <t>Rangos</t>
+  </si>
+  <si>
+    <r>
+      <t>Cantidad &gt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Precio &gt;= 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Descuento &gt;=0</t>
+    </r>
+  </si>
+  <si>
+    <t>Excel Odoo – Costos</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verificar columnas: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProductoID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CostoUnitario</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Impuesto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FechaCosto</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cada </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProductoID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del archivo de ventas debe tener costo asociado</t>
+    </r>
+  </si>
+  <si>
+    <t>JSON ETL</t>
+  </si>
+  <si>
+    <t>Mapeo</t>
+  </si>
+  <si>
+    <t>Campos JSON coinciden con dimensiones y hechos del modelo estrella</t>
+  </si>
+  <si>
+    <t>Cada ETL</t>
+  </si>
+  <si>
+    <t>Consistencia</t>
+  </si>
+  <si>
+    <t>Totales por fecha, producto y cliente coinciden con Excel</t>
+  </si>
+  <si>
+    <t>Integridad referencial</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cada </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VentaID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> debe existir en dimensión de ventas y sus claves foráneas en otras dimensiones</t>
+    </r>
+  </si>
+  <si>
+    <t>Reglas de negocio</t>
+  </si>
+  <si>
+    <t>Descuentos, impuestos, costos calculados según reglas de Odoo</t>
+  </si>
+  <si>
+    <t>Modelo relacional</t>
+  </si>
+  <si>
+    <r>
+      <t>Revisar FK entre hecho y dimensiones (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProductoID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ClienteID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FechaID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cada carga</t>
+  </si>
+  <si>
+    <t>Totales</t>
+  </si>
+  <si>
+    <t>Sumatoria de ventas y costos por periodo coincide con JSON</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>Totales y KPIs</t>
+  </si>
+  <si>
+    <r>
+      <t>Verificar que las medidas DAX (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SUMX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AVERAGEX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, margen`) reflejen datos correctos</t>
+    </r>
+  </si>
+  <si>
+    <t>Cada reporte / actualización</t>
+  </si>
+  <si>
+    <t>Filtros y segmentaciones</t>
+  </si>
+  <si>
+    <t>Validar que filtros por fecha, producto o región no alteren totales esperados</t>
+  </si>
+  <si>
+    <t>Alertas</t>
+  </si>
+  <si>
+    <t>Revisar errores de fórmula o valores inesperados</t>
   </si>
 </sst>
 </file>
@@ -2850,7 +3383,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2866,8 +3399,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2883,6 +3429,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2914,7 +3484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2926,6 +3496,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3231,7 +3819,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH723"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="30.7109375" customWidth="1"/>
     <col min="5" max="10" width="30.7109375" hidden="1" customWidth="1"/>
@@ -3257,7 +3845,7 @@
     <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3361,7 +3949,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -3418,7 +4006,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
@@ -3473,7 +4061,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -3528,7 +4116,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -3583,7 +4171,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -3642,7 +4230,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -3703,7 +4291,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34">
       <c r="A8" s="2" t="s">
         <v>43</v>
       </c>
@@ -3762,7 +4350,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -3821,7 +4409,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34">
       <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
@@ -3878,7 +4466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -3935,7 +4523,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34">
       <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
@@ -3992,7 +4580,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34">
       <c r="A13" s="2" t="s">
         <v>53</v>
       </c>
@@ -4049,7 +4637,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -4106,7 +4694,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34">
       <c r="A15" s="2"/>
       <c r="B15" s="2">
         <v>0</v>
@@ -4163,7 +4751,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34">
       <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
@@ -4220,7 +4808,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -4275,7 +4863,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23">
       <c r="A18" s="2"/>
       <c r="B18" s="2">
         <v>0</v>
@@ -4332,7 +4920,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="30">
       <c r="A19" s="2"/>
       <c r="B19" s="2">
         <v>0</v>
@@ -4387,7 +4975,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="30">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
@@ -4444,7 +5032,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="30">
       <c r="A21" s="2" t="s">
         <v>65</v>
       </c>
@@ -4501,7 +5089,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="30">
       <c r="A22" s="2" t="s">
         <v>66</v>
       </c>
@@ -4558,7 +5146,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23">
       <c r="A23" s="2" t="s">
         <v>67</v>
       </c>
@@ -4615,7 +5203,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="30">
       <c r="A24" s="2" t="s">
         <v>69</v>
       </c>
@@ -4672,7 +5260,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23">
       <c r="A25" s="2" t="s">
         <v>71</v>
       </c>
@@ -4729,7 +5317,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="30">
       <c r="A26" s="2" t="s">
         <v>71</v>
       </c>
@@ -4786,7 +5374,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="30">
       <c r="A27" s="2" t="s">
         <v>71</v>
       </c>
@@ -4843,7 +5431,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="30">
       <c r="A28" s="2" t="s">
         <v>73</v>
       </c>
@@ -4900,7 +5488,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="30">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -4957,7 +5545,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="30">
       <c r="A30" s="2" t="s">
         <v>75</v>
       </c>
@@ -5014,7 +5602,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23">
       <c r="A31" s="2" t="s">
         <v>75</v>
       </c>
@@ -5071,7 +5659,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="30">
       <c r="A32" s="2" t="s">
         <v>78</v>
       </c>
@@ -5128,7 +5716,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
@@ -5185,7 +5773,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23">
       <c r="A34" s="2" t="s">
         <v>81</v>
       </c>
@@ -5242,7 +5830,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23">
       <c r="A35" s="2" t="s">
         <v>82</v>
       </c>
@@ -5299,7 +5887,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23">
       <c r="A36" s="2" t="s">
         <v>83</v>
       </c>
@@ -5356,7 +5944,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23">
       <c r="A37" s="2" t="s">
         <v>84</v>
       </c>
@@ -5413,7 +6001,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23">
       <c r="A38" s="2" t="s">
         <v>86</v>
       </c>
@@ -5470,7 +6058,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23">
       <c r="A39" s="2" t="s">
         <v>88</v>
       </c>
@@ -5527,7 +6115,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23">
       <c r="A40" s="2" t="s">
         <v>90</v>
       </c>
@@ -5584,7 +6172,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23">
       <c r="A41" s="2" t="s">
         <v>92</v>
       </c>
@@ -5641,7 +6229,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23">
       <c r="A42" s="2" t="s">
         <v>93</v>
       </c>
@@ -5698,7 +6286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="30">
       <c r="A43" s="2" t="s">
         <v>94</v>
       </c>
@@ -5755,7 +6343,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23">
       <c r="A44" s="2" t="s">
         <v>96</v>
       </c>
@@ -5812,7 +6400,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23">
       <c r="A45" s="2" t="s">
         <v>96</v>
       </c>
@@ -5869,7 +6457,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="30">
       <c r="A46" s="2" t="s">
         <v>97</v>
       </c>
@@ -5926,7 +6514,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="30">
       <c r="A47" s="2" t="s">
         <v>99</v>
       </c>
@@ -5983,7 +6571,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="30">
       <c r="A48" s="2" t="s">
         <v>100</v>
       </c>
@@ -6040,7 +6628,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23">
       <c r="A49" s="2" t="s">
         <v>101</v>
       </c>
@@ -6097,7 +6685,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23">
       <c r="A50" s="2" t="s">
         <v>103</v>
       </c>
@@ -6154,7 +6742,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23">
       <c r="A51" s="2" t="s">
         <v>105</v>
       </c>
@@ -6211,7 +6799,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23">
       <c r="A52" s="2" t="s">
         <v>106</v>
       </c>
@@ -6268,7 +6856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="30">
       <c r="A53" s="2" t="s">
         <v>107</v>
       </c>
@@ -6325,7 +6913,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23">
       <c r="A54" s="2" t="s">
         <v>109</v>
       </c>
@@ -6382,7 +6970,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="30">
       <c r="A55" s="2" t="s">
         <v>111</v>
       </c>
@@ -6439,7 +7027,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23">
       <c r="A56" s="2" t="s">
         <v>113</v>
       </c>
@@ -6496,7 +7084,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="30">
       <c r="A57" s="2" t="s">
         <v>115</v>
       </c>
@@ -6553,7 +7141,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" ht="30">
       <c r="A58" s="2" t="s">
         <v>117</v>
       </c>
@@ -6610,7 +7198,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" ht="30">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
@@ -6667,7 +7255,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="30">
       <c r="A60" s="2" t="s">
         <v>119</v>
       </c>
@@ -6724,7 +7312,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="30">
       <c r="A61" s="2" t="s">
         <v>121</v>
       </c>
@@ -6781,7 +7369,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23">
       <c r="A62" s="2" t="s">
         <v>122</v>
       </c>
@@ -6838,7 +7426,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23">
       <c r="A63" s="2" t="s">
         <v>124</v>
       </c>
@@ -6895,7 +7483,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23">
       <c r="A64" s="2" t="s">
         <v>125</v>
       </c>
@@ -6952,7 +7540,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23">
       <c r="A65" s="2" t="s">
         <v>126</v>
       </c>
@@ -7009,7 +7597,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23">
       <c r="A66" s="2" t="s">
         <v>127</v>
       </c>
@@ -7066,7 +7654,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23">
       <c r="A67" s="2" t="s">
         <v>129</v>
       </c>
@@ -7123,7 +7711,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23">
       <c r="A68" s="2" t="s">
         <v>130</v>
       </c>
@@ -7180,7 +7768,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23">
       <c r="A69" s="2" t="s">
         <v>132</v>
       </c>
@@ -7237,7 +7825,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23">
       <c r="A70" s="2" t="s">
         <v>133</v>
       </c>
@@ -7294,7 +7882,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23">
       <c r="A71" s="2" t="s">
         <v>134</v>
       </c>
@@ -7351,7 +7939,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23">
       <c r="A72" s="2" t="s">
         <v>135</v>
       </c>
@@ -7408,7 +7996,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23">
       <c r="A73" s="2" t="s">
         <v>137</v>
       </c>
@@ -7465,7 +8053,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23">
       <c r="A74" s="2" t="s">
         <v>137</v>
       </c>
@@ -7522,7 +8110,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23">
       <c r="A75" s="2" t="s">
         <v>139</v>
       </c>
@@ -7579,7 +8167,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23">
       <c r="A76" s="2" t="s">
         <v>139</v>
       </c>
@@ -7636,7 +8224,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23">
       <c r="A77" s="2" t="s">
         <v>139</v>
       </c>
@@ -7693,7 +8281,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23">
       <c r="A78" s="2" t="s">
         <v>141</v>
       </c>
@@ -7750,7 +8338,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23">
       <c r="A79" s="2" t="s">
         <v>141</v>
       </c>
@@ -7807,7 +8395,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23">
       <c r="A80" s="2" t="s">
         <v>141</v>
       </c>
@@ -7864,7 +8452,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23">
       <c r="A81" s="2" t="s">
         <v>141</v>
       </c>
@@ -7921,7 +8509,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" ht="30">
       <c r="A82" s="2" t="s">
         <v>142</v>
       </c>
@@ -7978,7 +8566,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23">
       <c r="A83" s="2" t="s">
         <v>144</v>
       </c>
@@ -8035,7 +8623,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23">
       <c r="A84" s="2" t="s">
         <v>146</v>
       </c>
@@ -8092,7 +8680,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" ht="30">
       <c r="A85" s="2" t="s">
         <v>148</v>
       </c>
@@ -8149,7 +8737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23">
       <c r="A86" s="2" t="s">
         <v>150</v>
       </c>
@@ -8206,7 +8794,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23">
       <c r="A87" s="2" t="s">
         <v>151</v>
       </c>
@@ -8263,7 +8851,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23">
       <c r="A88" s="2" t="s">
         <v>153</v>
       </c>
@@ -8320,7 +8908,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23">
       <c r="A89" s="2" t="s">
         <v>155</v>
       </c>
@@ -8377,7 +8965,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" ht="45">
       <c r="A90" s="2" t="s">
         <v>157</v>
       </c>
@@ -8434,7 +9022,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23">
       <c r="A91" s="2" t="s">
         <v>159</v>
       </c>
@@ -8491,7 +9079,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23">
       <c r="A92" s="2" t="s">
         <v>161</v>
       </c>
@@ -8548,7 +9136,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23">
       <c r="A93" s="2" t="s">
         <v>163</v>
       </c>
@@ -8605,7 +9193,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" ht="30">
       <c r="A94" s="2" t="s">
         <v>164</v>
       </c>
@@ -8662,7 +9250,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" ht="30">
       <c r="A95" s="2" t="s">
         <v>166</v>
       </c>
@@ -8719,7 +9307,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" ht="30">
       <c r="A96" s="2" t="s">
         <v>168</v>
       </c>
@@ -8776,7 +9364,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23">
       <c r="A97" s="2" t="s">
         <v>169</v>
       </c>
@@ -8833,7 +9421,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" ht="45">
       <c r="A98" s="2" t="s">
         <v>171</v>
       </c>
@@ -8890,7 +9478,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23">
       <c r="A99" s="2" t="s">
         <v>173</v>
       </c>
@@ -8947,7 +9535,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23">
       <c r="A100" s="2" t="s">
         <v>175</v>
       </c>
@@ -9004,7 +9592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23">
       <c r="A101" s="2" t="s">
         <v>177</v>
       </c>
@@ -9061,7 +9649,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23">
       <c r="A102" s="2" t="s">
         <v>179</v>
       </c>
@@ -9118,7 +9706,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23">
       <c r="A103" s="2" t="s">
         <v>181</v>
       </c>
@@ -9175,7 +9763,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23">
       <c r="A104" s="2" t="s">
         <v>182</v>
       </c>
@@ -9232,7 +9820,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" ht="30">
       <c r="A105" s="2" t="s">
         <v>184</v>
       </c>
@@ -9287,7 +9875,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" ht="30">
       <c r="A106" s="2" t="s">
         <v>185</v>
       </c>
@@ -9344,7 +9932,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23" ht="30">
       <c r="A107" s="2" t="s">
         <v>186</v>
       </c>
@@ -9401,7 +9989,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" ht="30">
       <c r="A108" s="2" t="s">
         <v>187</v>
       </c>
@@ -9458,7 +10046,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="109" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23" ht="30">
       <c r="A109" s="2" t="s">
         <v>188</v>
       </c>
@@ -9515,7 +10103,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" ht="30">
       <c r="A110" s="2" t="s">
         <v>189</v>
       </c>
@@ -9572,7 +10160,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" ht="30">
       <c r="A111" s="2" t="s">
         <v>191</v>
       </c>
@@ -9629,7 +10217,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23" ht="30">
       <c r="A112" s="2" t="s">
         <v>192</v>
       </c>
@@ -9686,7 +10274,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23">
       <c r="A113" s="2" t="s">
         <v>192</v>
       </c>
@@ -9743,7 +10331,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" ht="30">
       <c r="A114" s="2" t="s">
         <v>193</v>
       </c>
@@ -9800,7 +10388,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23" ht="30">
       <c r="A115" s="2" t="s">
         <v>194</v>
       </c>
@@ -9857,7 +10445,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23" ht="30">
       <c r="A116" s="2" t="s">
         <v>195</v>
       </c>
@@ -9914,7 +10502,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23">
       <c r="A117" s="2" t="s">
         <v>196</v>
       </c>
@@ -9971,7 +10559,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" ht="30">
       <c r="A118" s="2" t="s">
         <v>197</v>
       </c>
@@ -10028,7 +10616,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" ht="30">
       <c r="A119" s="2" t="s">
         <v>199</v>
       </c>
@@ -10085,7 +10673,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23" ht="30">
       <c r="A120" s="2" t="s">
         <v>200</v>
       </c>
@@ -10142,7 +10730,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23">
       <c r="A121" s="2" t="s">
         <v>202</v>
       </c>
@@ -10199,7 +10787,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23">
       <c r="A122" s="2" t="s">
         <v>203</v>
       </c>
@@ -10256,7 +10844,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23">
       <c r="A123" s="2" t="s">
         <v>205</v>
       </c>
@@ -10313,7 +10901,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23">
       <c r="A124" s="2" t="s">
         <v>207</v>
       </c>
@@ -10370,7 +10958,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23">
       <c r="A125" s="2" t="s">
         <v>209</v>
       </c>
@@ -10427,7 +11015,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23">
       <c r="A126" s="2" t="s">
         <v>210</v>
       </c>
@@ -10484,7 +11072,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23">
       <c r="A127" s="2" t="s">
         <v>211</v>
       </c>
@@ -10541,7 +11129,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23">
       <c r="A128" s="2" t="s">
         <v>212</v>
       </c>
@@ -10598,7 +11186,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23">
       <c r="A129" s="2" t="s">
         <v>214</v>
       </c>
@@ -10655,7 +11243,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23">
       <c r="A130" s="2" t="s">
         <v>215</v>
       </c>
@@ -10712,7 +11300,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23">
       <c r="A131" s="2" t="s">
         <v>216</v>
       </c>
@@ -10769,7 +11357,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23">
       <c r="A132" s="2" t="s">
         <v>217</v>
       </c>
@@ -10826,7 +11414,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23">
       <c r="A133" s="2" t="s">
         <v>218</v>
       </c>
@@ -10883,7 +11471,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23">
       <c r="A134" s="2" t="s">
         <v>219</v>
       </c>
@@ -10940,7 +11528,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23">
       <c r="A135" s="2" t="s">
         <v>220</v>
       </c>
@@ -10997,7 +11585,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23">
       <c r="A136" s="2" t="s">
         <v>221</v>
       </c>
@@ -11054,7 +11642,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23">
       <c r="A137" s="2" t="s">
         <v>222</v>
       </c>
@@ -11111,7 +11699,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23">
       <c r="A138" s="2" t="s">
         <v>223</v>
       </c>
@@ -11168,7 +11756,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23">
       <c r="A139" s="2" t="s">
         <v>224</v>
       </c>
@@ -11225,7 +11813,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23">
       <c r="A140" s="2" t="s">
         <v>225</v>
       </c>
@@ -11282,7 +11870,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23">
       <c r="A141" s="2" t="s">
         <v>226</v>
       </c>
@@ -11339,7 +11927,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23">
       <c r="A142" s="2" t="s">
         <v>226</v>
       </c>
@@ -11396,7 +11984,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23">
       <c r="A143" s="2" t="s">
         <v>227</v>
       </c>
@@ -11453,7 +12041,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23" ht="30">
       <c r="A144" s="2" t="s">
         <v>229</v>
       </c>
@@ -11510,7 +12098,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23">
       <c r="A145" s="2" t="s">
         <v>231</v>
       </c>
@@ -11567,7 +12155,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23">
       <c r="A146" s="2" t="s">
         <v>232</v>
       </c>
@@ -11624,7 +12212,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23">
       <c r="A147" s="2" t="s">
         <v>232</v>
       </c>
@@ -11681,7 +12269,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23">
       <c r="A148" s="2" t="s">
         <v>232</v>
       </c>
@@ -11738,7 +12326,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:23">
       <c r="A149" s="2" t="s">
         <v>233</v>
       </c>
@@ -11795,7 +12383,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23">
       <c r="A150" s="2" t="s">
         <v>233</v>
       </c>
@@ -11852,7 +12440,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23" ht="30">
       <c r="A151" s="2" t="s">
         <v>234</v>
       </c>
@@ -11909,7 +12497,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23">
       <c r="A152" s="2" t="s">
         <v>235</v>
       </c>
@@ -11966,7 +12554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23">
       <c r="A153" s="2" t="s">
         <v>237</v>
       </c>
@@ -12023,7 +12611,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="154" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23" ht="30">
       <c r="A154" s="2" t="s">
         <v>238</v>
       </c>
@@ -12080,7 +12668,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23">
       <c r="A155" s="2" t="s">
         <v>240</v>
       </c>
@@ -12137,7 +12725,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23" ht="30">
       <c r="A156" s="2" t="s">
         <v>242</v>
       </c>
@@ -12194,7 +12782,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23" ht="30">
       <c r="A157" s="2" t="s">
         <v>243</v>
       </c>
@@ -12251,7 +12839,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23" ht="30">
       <c r="A158" s="2" t="s">
         <v>244</v>
       </c>
@@ -12308,7 +12896,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23" ht="30">
       <c r="A159" s="2" t="s">
         <v>245</v>
       </c>
@@ -12365,7 +12953,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23">
       <c r="A160" s="2" t="s">
         <v>246</v>
       </c>
@@ -12422,7 +13010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23">
       <c r="A161" s="2" t="s">
         <v>248</v>
       </c>
@@ -12479,7 +13067,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23">
       <c r="A162" s="2" t="s">
         <v>177</v>
       </c>
@@ -12536,7 +13124,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23">
       <c r="A163" s="2" t="s">
         <v>249</v>
       </c>
@@ -12593,7 +13181,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23">
       <c r="A164" s="2"/>
       <c r="B164" s="2">
         <v>0</v>
@@ -12648,7 +13236,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" ht="30">
       <c r="A165" s="2" t="s">
         <v>253</v>
       </c>
@@ -12705,7 +13293,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23">
       <c r="A166" s="2" t="s">
         <v>254</v>
       </c>
@@ -12762,7 +13350,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23">
       <c r="A167" s="2" t="s">
         <v>255</v>
       </c>
@@ -12819,7 +13407,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23">
       <c r="A168" s="2" t="s">
         <v>256</v>
       </c>
@@ -12876,7 +13464,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23">
       <c r="A169" s="2" t="s">
         <v>258</v>
       </c>
@@ -12933,7 +13521,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23">
       <c r="A170" s="2" t="s">
         <v>260</v>
       </c>
@@ -12990,7 +13578,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23">
       <c r="A171" s="2" t="s">
         <v>261</v>
       </c>
@@ -13047,7 +13635,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23">
       <c r="A172" s="2" t="s">
         <v>262</v>
       </c>
@@ -13104,7 +13692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" ht="30">
       <c r="A173" s="2" t="s">
         <v>264</v>
       </c>
@@ -13161,7 +13749,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23">
       <c r="A174" s="2" t="s">
         <v>265</v>
       </c>
@@ -13218,7 +13806,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23">
       <c r="A175" s="2" t="s">
         <v>267</v>
       </c>
@@ -13275,7 +13863,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23">
       <c r="A176" s="2" t="s">
         <v>268</v>
       </c>
@@ -13332,7 +13920,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23">
       <c r="A177" s="2" t="s">
         <v>269</v>
       </c>
@@ -13389,7 +13977,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23">
       <c r="A178" s="2" t="s">
         <v>271</v>
       </c>
@@ -13446,7 +14034,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23">
       <c r="A179" s="2" t="s">
         <v>272</v>
       </c>
@@ -13503,7 +14091,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23">
       <c r="A180" s="2" t="s">
         <v>273</v>
       </c>
@@ -13560,7 +14148,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23">
       <c r="A181" s="2" t="s">
         <v>274</v>
       </c>
@@ -13617,7 +14205,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23">
       <c r="A182" s="2" t="s">
         <v>276</v>
       </c>
@@ -13674,7 +14262,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:23">
       <c r="A183" s="2" t="s">
         <v>277</v>
       </c>
@@ -13731,7 +14319,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23">
       <c r="A184" s="2" t="s">
         <v>278</v>
       </c>
@@ -13788,7 +14376,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:23">
       <c r="A185" s="2" t="s">
         <v>279</v>
       </c>
@@ -13845,7 +14433,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:23">
       <c r="A186" s="2" t="s">
         <v>280</v>
       </c>
@@ -13902,7 +14490,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:23">
       <c r="A187" s="2" t="s">
         <v>281</v>
       </c>
@@ -13959,7 +14547,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23">
       <c r="A188" s="2" t="s">
         <v>282</v>
       </c>
@@ -14016,7 +14604,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23">
       <c r="A189" s="2" t="s">
         <v>283</v>
       </c>
@@ -14073,7 +14661,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:23">
       <c r="A190" s="2" t="s">
         <v>285</v>
       </c>
@@ -14130,7 +14718,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23">
       <c r="A191" s="2" t="s">
         <v>286</v>
       </c>
@@ -14187,7 +14775,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23">
       <c r="A192" s="2" t="s">
         <v>288</v>
       </c>
@@ -14244,7 +14832,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23">
       <c r="A193" s="2" t="s">
         <v>289</v>
       </c>
@@ -14301,7 +14889,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23">
       <c r="A194" s="2" t="s">
         <v>290</v>
       </c>
@@ -14358,7 +14946,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23">
       <c r="A195" s="2" t="s">
         <v>292</v>
       </c>
@@ -14415,7 +15003,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23">
       <c r="A196" s="2" t="s">
         <v>294</v>
       </c>
@@ -14472,7 +15060,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23">
       <c r="A197" s="2" t="s">
         <v>295</v>
       </c>
@@ -14529,7 +15117,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23">
       <c r="A198" s="2" t="s">
         <v>296</v>
       </c>
@@ -14586,7 +15174,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23">
       <c r="A199" s="2" t="s">
         <v>297</v>
       </c>
@@ -14643,7 +15231,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23">
       <c r="A200" s="2" t="s">
         <v>297</v>
       </c>
@@ -14700,7 +15288,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="201" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:23" ht="30">
       <c r="A201" s="2" t="s">
         <v>299</v>
       </c>
@@ -14757,7 +15345,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23">
       <c r="A202" s="2" t="s">
         <v>301</v>
       </c>
@@ -14814,7 +15402,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23">
       <c r="A203" s="2" t="s">
         <v>302</v>
       </c>
@@ -14871,7 +15459,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23">
       <c r="A204" s="2" t="s">
         <v>302</v>
       </c>
@@ -14928,7 +15516,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23">
       <c r="A205" s="2" t="s">
         <v>302</v>
       </c>
@@ -14985,7 +15573,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23" ht="30">
       <c r="A206" s="2" t="s">
         <v>303</v>
       </c>
@@ -15042,7 +15630,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23" ht="30">
       <c r="A207" s="2" t="s">
         <v>304</v>
       </c>
@@ -15099,7 +15687,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23">
       <c r="A208" s="2" t="s">
         <v>305</v>
       </c>
@@ -15156,7 +15744,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="209" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:23" ht="30">
       <c r="A209" s="2" t="s">
         <v>306</v>
       </c>
@@ -15213,7 +15801,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:23">
       <c r="A210" s="2" t="s">
         <v>308</v>
       </c>
@@ -15270,7 +15858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23">
       <c r="A211" s="2" t="s">
         <v>309</v>
       </c>
@@ -15327,7 +15915,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="212" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23" ht="30">
       <c r="A212" s="2" t="s">
         <v>310</v>
       </c>
@@ -15384,7 +15972,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:23">
       <c r="A213" s="2" t="s">
         <v>312</v>
       </c>
@@ -15441,7 +16029,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:23">
       <c r="A214" s="2" t="s">
         <v>313</v>
       </c>
@@ -15498,7 +16086,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:23">
       <c r="A215" s="2" t="s">
         <v>314</v>
       </c>
@@ -15555,7 +16143,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="216" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:23" ht="30">
       <c r="A216" s="2" t="s">
         <v>316</v>
       </c>
@@ -15612,7 +16200,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" ht="30">
       <c r="A217" s="2" t="s">
         <v>316</v>
       </c>
@@ -15669,7 +16257,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23">
       <c r="A218" s="2" t="s">
         <v>318</v>
       </c>
@@ -15726,7 +16314,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23">
       <c r="A219" s="2" t="s">
         <v>319</v>
       </c>
@@ -15783,7 +16371,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23">
       <c r="A220" s="2" t="s">
         <v>320</v>
       </c>
@@ -15840,7 +16428,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23">
       <c r="A221" s="2" t="s">
         <v>321</v>
       </c>
@@ -15897,7 +16485,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" ht="30">
       <c r="A222" s="2" t="s">
         <v>322</v>
       </c>
@@ -15954,7 +16542,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23">
       <c r="A223" s="2" t="s">
         <v>323</v>
       </c>
@@ -16011,7 +16599,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="224" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:23" ht="30">
       <c r="A224" s="2" t="s">
         <v>325</v>
       </c>
@@ -16068,7 +16656,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23">
       <c r="A225" s="2" t="s">
         <v>327</v>
       </c>
@@ -16125,7 +16713,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23">
       <c r="A226" s="2" t="s">
         <v>329</v>
       </c>
@@ -16182,7 +16770,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23">
       <c r="A227" s="2" t="s">
         <v>330</v>
       </c>
@@ -16239,7 +16827,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23">
       <c r="A228" s="2" t="s">
         <v>331</v>
       </c>
@@ -16296,7 +16884,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23">
       <c r="A229" s="2" t="s">
         <v>332</v>
       </c>
@@ -16353,7 +16941,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23">
       <c r="A230" s="2" t="s">
         <v>333</v>
       </c>
@@ -16410,7 +16998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23">
       <c r="A231" s="2" t="s">
         <v>334</v>
       </c>
@@ -16467,7 +17055,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23">
       <c r="A232" s="2" t="s">
         <v>336</v>
       </c>
@@ -16524,7 +17112,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23">
       <c r="A233" s="2" t="s">
         <v>337</v>
       </c>
@@ -16581,7 +17169,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23">
       <c r="A234" s="2" t="s">
         <v>339</v>
       </c>
@@ -16638,7 +17226,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23">
       <c r="A235" s="2" t="s">
         <v>341</v>
       </c>
@@ -16695,7 +17283,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23">
       <c r="A236" s="2" t="s">
         <v>342</v>
       </c>
@@ -16752,7 +17340,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23">
       <c r="A237" s="2" t="s">
         <v>344</v>
       </c>
@@ -16809,7 +17397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23">
       <c r="A238" s="2" t="s">
         <v>345</v>
       </c>
@@ -16866,7 +17454,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23">
       <c r="A239" s="2" t="s">
         <v>346</v>
       </c>
@@ -16923,7 +17511,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23">
       <c r="A240" s="2" t="s">
         <v>347</v>
       </c>
@@ -16980,7 +17568,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23">
       <c r="A241" s="2" t="s">
         <v>348</v>
       </c>
@@ -17037,7 +17625,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23">
       <c r="A242" s="2" t="s">
         <v>349</v>
       </c>
@@ -17094,7 +17682,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" ht="30">
       <c r="A243" s="2" t="s">
         <v>350</v>
       </c>
@@ -17151,7 +17739,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23" ht="30">
       <c r="A244" s="2" t="s">
         <v>352</v>
       </c>
@@ -17208,7 +17796,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:23" ht="30">
       <c r="A245" s="2" t="s">
         <v>354</v>
       </c>
@@ -17265,7 +17853,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:23">
       <c r="A246" s="2" t="s">
         <v>356</v>
       </c>
@@ -17322,7 +17910,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:23">
       <c r="A247" s="2" t="s">
         <v>357</v>
       </c>
@@ -17379,7 +17967,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:23">
       <c r="A248" s="2" t="s">
         <v>358</v>
       </c>
@@ -17436,7 +18024,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23">
       <c r="A249" s="2" t="s">
         <v>359</v>
       </c>
@@ -17493,7 +18081,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:23">
       <c r="A250" s="2" t="s">
         <v>360</v>
       </c>
@@ -17550,7 +18138,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:23">
       <c r="A251" s="2" t="s">
         <v>361</v>
       </c>
@@ -17607,7 +18195,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23">
       <c r="A252" s="2" t="s">
         <v>362</v>
       </c>
@@ -17664,7 +18252,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23">
       <c r="A253" s="2" t="s">
         <v>363</v>
       </c>
@@ -17721,7 +18309,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:23">
       <c r="A254" s="2" t="s">
         <v>365</v>
       </c>
@@ -17778,7 +18366,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="255" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:23" ht="30">
       <c r="A255" s="2" t="s">
         <v>367</v>
       </c>
@@ -17835,7 +18423,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23" ht="30">
       <c r="A256" s="2" t="s">
         <v>368</v>
       </c>
@@ -17892,7 +18480,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:23">
       <c r="A257" s="2" t="s">
         <v>150</v>
       </c>
@@ -17949,7 +18537,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:23">
       <c r="A258" s="2" t="s">
         <v>371</v>
       </c>
@@ -18006,7 +18594,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:23">
       <c r="A259" s="2" t="s">
         <v>372</v>
       </c>
@@ -18063,7 +18651,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="260" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:23" ht="30">
       <c r="A260" s="2" t="s">
         <v>373</v>
       </c>
@@ -18120,7 +18708,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="261" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:23" ht="30">
       <c r="A261" s="2" t="s">
         <v>374</v>
       </c>
@@ -18177,7 +18765,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23">
       <c r="A262" s="2" t="s">
         <v>375</v>
       </c>
@@ -18234,7 +18822,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:23">
       <c r="A263" s="2" t="s">
         <v>377</v>
       </c>
@@ -18291,7 +18879,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="30">
       <c r="A264" s="2" t="s">
         <v>378</v>
       </c>
@@ -18348,7 +18936,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:23">
       <c r="A265" s="2" t="s">
         <v>379</v>
       </c>
@@ -18405,7 +18993,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23">
       <c r="A266" s="2" t="s">
         <v>381</v>
       </c>
@@ -18462,7 +19050,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:23">
       <c r="A267" s="2" t="s">
         <v>246</v>
       </c>
@@ -18519,7 +19107,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:23">
       <c r="A268" s="2" t="s">
         <v>246</v>
       </c>
@@ -18576,7 +19164,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23">
       <c r="A269" s="2" t="s">
         <v>384</v>
       </c>
@@ -18633,7 +19221,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23">
       <c r="A270" s="2" t="s">
         <v>385</v>
       </c>
@@ -18690,7 +19278,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" ht="30">
       <c r="A271" s="2" t="s">
         <v>386</v>
       </c>
@@ -18747,7 +19335,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="30">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
@@ -18804,7 +19392,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23">
       <c r="A273" s="2" t="s">
         <v>388</v>
       </c>
@@ -18861,7 +19449,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:23">
       <c r="A274" s="2" t="s">
         <v>390</v>
       </c>
@@ -18918,7 +19506,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:23">
       <c r="A275" s="2" t="s">
         <v>391</v>
       </c>
@@ -18975,7 +19563,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23">
       <c r="A276" s="2" t="s">
         <v>393</v>
       </c>
@@ -19032,7 +19620,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23">
       <c r="A277" s="2" t="s">
         <v>394</v>
       </c>
@@ -19089,7 +19677,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23" ht="30">
       <c r="A278" s="2" t="s">
         <v>395</v>
       </c>
@@ -19146,7 +19734,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:23" ht="30">
       <c r="A279" s="2" t="s">
         <v>396</v>
       </c>
@@ -19203,7 +19791,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23">
       <c r="A280" s="2" t="s">
         <v>398</v>
       </c>
@@ -19260,7 +19848,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:23">
       <c r="A281" s="2" t="s">
         <v>400</v>
       </c>
@@ -19317,7 +19905,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:23">
       <c r="A282" s="2" t="s">
         <v>402</v>
       </c>
@@ -19374,7 +19962,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:23">
       <c r="A283" s="2" t="s">
         <v>404</v>
       </c>
@@ -19431,7 +20019,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:23">
       <c r="A284" s="2" t="s">
         <v>405</v>
       </c>
@@ -19488,7 +20076,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23">
       <c r="A285" s="2" t="s">
         <v>406</v>
       </c>
@@ -19545,7 +20133,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23">
       <c r="A286" s="2" t="s">
         <v>407</v>
       </c>
@@ -19602,7 +20190,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23">
       <c r="A287" s="2" t="s">
         <v>408</v>
       </c>
@@ -19659,7 +20247,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23">
       <c r="A288" s="2" t="s">
         <v>410</v>
       </c>
@@ -19716,7 +20304,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23">
       <c r="A289" s="2" t="s">
         <v>411</v>
       </c>
@@ -19773,7 +20361,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23">
       <c r="A290" s="2" t="s">
         <v>412</v>
       </c>
@@ -19830,7 +20418,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:23">
       <c r="A291" s="2" t="s">
         <v>413</v>
       </c>
@@ -19887,7 +20475,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:23">
       <c r="A292" s="2" t="s">
         <v>415</v>
       </c>
@@ -19944,7 +20532,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:23">
       <c r="A293" s="2" t="s">
         <v>417</v>
       </c>
@@ -20001,7 +20589,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:23">
       <c r="A294" s="2" t="s">
         <v>418</v>
       </c>
@@ -20058,7 +20646,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="295" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:23" ht="30">
       <c r="A295" s="2" t="s">
         <v>419</v>
       </c>
@@ -20115,7 +20703,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:23">
       <c r="A296" s="2" t="s">
         <v>421</v>
       </c>
@@ -20172,7 +20760,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23">
       <c r="A297" s="2" t="s">
         <v>422</v>
       </c>
@@ -20229,7 +20817,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:23">
       <c r="A298" s="2" t="s">
         <v>423</v>
       </c>
@@ -20286,7 +20874,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23">
       <c r="A299" s="2" t="s">
         <v>424</v>
       </c>
@@ -20343,7 +20931,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:23">
       <c r="A300" s="2" t="s">
         <v>426</v>
       </c>
@@ -20400,7 +20988,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:23">
       <c r="A301" s="2" t="s">
         <v>427</v>
       </c>
@@ -20457,7 +21045,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:23">
       <c r="A302" s="2" t="s">
         <v>428</v>
       </c>
@@ -20514,7 +21102,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:23" ht="30">
       <c r="A303" s="2" t="s">
         <v>430</v>
       </c>
@@ -20571,7 +21159,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:23">
       <c r="A304" s="2" t="s">
         <v>432</v>
       </c>
@@ -20628,7 +21216,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:23">
       <c r="A305" s="2" t="s">
         <v>434</v>
       </c>
@@ -20685,7 +21273,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:23" ht="30">
       <c r="A306" s="2" t="s">
         <v>436</v>
       </c>
@@ -20742,7 +21330,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:23">
       <c r="A307" s="2" t="s">
         <v>437</v>
       </c>
@@ -20799,7 +21387,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:23">
       <c r="A308" s="2" t="s">
         <v>438</v>
       </c>
@@ -20856,7 +21444,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:23">
       <c r="A309" s="2" t="s">
         <v>440</v>
       </c>
@@ -20913,7 +21501,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:23">
       <c r="A310" s="2" t="s">
         <v>442</v>
       </c>
@@ -20970,7 +21558,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:23">
       <c r="A311" s="2" t="s">
         <v>443</v>
       </c>
@@ -21027,7 +21615,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:23">
       <c r="A312" s="2" t="s">
         <v>444</v>
       </c>
@@ -21084,7 +21672,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:23">
       <c r="A313" s="2" t="s">
         <v>445</v>
       </c>
@@ -21141,7 +21729,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:23">
       <c r="A314" s="2" t="s">
         <v>446</v>
       </c>
@@ -21198,7 +21786,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:23">
       <c r="A315" s="2" t="s">
         <v>447</v>
       </c>
@@ -21255,7 +21843,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:23">
       <c r="A316" s="2" t="s">
         <v>448</v>
       </c>
@@ -21312,7 +21900,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:23">
       <c r="A317" s="2" t="s">
         <v>449</v>
       </c>
@@ -21369,7 +21957,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:23">
       <c r="A318" s="2" t="s">
         <v>450</v>
       </c>
@@ -21426,7 +22014,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:23">
       <c r="A319" s="2" t="s">
         <v>451</v>
       </c>
@@ -21483,7 +22071,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:23">
       <c r="A320" s="2" t="s">
         <v>452</v>
       </c>
@@ -21540,7 +22128,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:23">
       <c r="A321" s="2" t="s">
         <v>453</v>
       </c>
@@ -21597,7 +22185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:23">
       <c r="A322" s="2" t="s">
         <v>454</v>
       </c>
@@ -21654,7 +22242,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:23">
       <c r="A323" s="2" t="s">
         <v>456</v>
       </c>
@@ -21711,7 +22299,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:23" ht="30">
       <c r="A324" s="2" t="s">
         <v>457</v>
       </c>
@@ -21768,7 +22356,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:23" ht="30">
       <c r="A325" s="2" t="s">
         <v>458</v>
       </c>
@@ -21825,7 +22413,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:23">
       <c r="A326" s="2" t="s">
         <v>459</v>
       </c>
@@ -21882,7 +22470,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:23">
       <c r="A327" s="2" t="s">
         <v>461</v>
       </c>
@@ -21939,7 +22527,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:23">
       <c r="A328" s="2" t="s">
         <v>463</v>
       </c>
@@ -21996,7 +22584,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:23">
       <c r="A329" s="2" t="s">
         <v>464</v>
       </c>
@@ -22053,7 +22641,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:23">
       <c r="A330" s="2" t="s">
         <v>465</v>
       </c>
@@ -22110,7 +22698,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:23">
       <c r="A331" s="2" t="s">
         <v>466</v>
       </c>
@@ -22167,7 +22755,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:23">
       <c r="A332" s="2" t="s">
         <v>468</v>
       </c>
@@ -22224,7 +22812,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:23">
       <c r="A333" s="2" t="s">
         <v>469</v>
       </c>
@@ -22281,7 +22869,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:23">
       <c r="A334" s="2" t="s">
         <v>471</v>
       </c>
@@ -22338,7 +22926,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:23" ht="45">
       <c r="A335" s="2" t="s">
         <v>473</v>
       </c>
@@ -22395,7 +22983,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:23">
       <c r="A336" s="2" t="s">
         <v>473</v>
       </c>
@@ -22452,7 +23040,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:23">
       <c r="A337" s="2" t="s">
         <v>475</v>
       </c>
@@ -22509,7 +23097,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:23">
       <c r="A338" s="2" t="s">
         <v>476</v>
       </c>
@@ -22566,7 +23154,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="339" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:23" ht="30">
       <c r="A339" s="2" t="s">
         <v>478</v>
       </c>
@@ -22623,7 +23211,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:23">
       <c r="A340" s="2" t="s">
         <v>479</v>
       </c>
@@ -22680,7 +23268,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:23">
       <c r="A341" s="2" t="s">
         <v>481</v>
       </c>
@@ -22737,7 +23325,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:23">
       <c r="A342" s="2" t="s">
         <v>483</v>
       </c>
@@ -22794,7 +23382,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:23">
       <c r="A343" s="2" t="s">
         <v>484</v>
       </c>
@@ -22851,7 +23439,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:23">
       <c r="A344" s="2" t="s">
         <v>485</v>
       </c>
@@ -22908,7 +23496,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:23">
       <c r="A345" s="2" t="s">
         <v>486</v>
       </c>
@@ -22965,7 +23553,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:23">
       <c r="A346" s="2" t="s">
         <v>246</v>
       </c>
@@ -23022,7 +23610,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:23">
       <c r="A347" s="2" t="s">
         <v>487</v>
       </c>
@@ -23079,7 +23667,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:23">
       <c r="A348" s="2" t="s">
         <v>488</v>
       </c>
@@ -23136,7 +23724,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:23" ht="30">
       <c r="A349" s="2" t="s">
         <v>489</v>
       </c>
@@ -23193,7 +23781,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:23" ht="30">
       <c r="A350" s="2" t="s">
         <v>490</v>
       </c>
@@ -23250,7 +23838,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:23" ht="30">
       <c r="A351" s="2" t="s">
         <v>187</v>
       </c>
@@ -23307,7 +23895,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:23" ht="30">
       <c r="A352" s="2" t="s">
         <v>492</v>
       </c>
@@ -23364,7 +23952,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="353" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:23">
       <c r="A353" s="2" t="s">
         <v>493</v>
       </c>
@@ -23421,7 +24009,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="354" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:23">
       <c r="A354" s="2" t="s">
         <v>495</v>
       </c>
@@ -23478,7 +24066,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="355" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:23">
       <c r="A355" s="2" t="s">
         <v>496</v>
       </c>
@@ -23535,7 +24123,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:23">
       <c r="A356" s="2" t="s">
         <v>497</v>
       </c>
@@ -23592,7 +24180,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="357" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:23">
       <c r="A357" s="2" t="s">
         <v>498</v>
       </c>
@@ -23649,7 +24237,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:23" ht="30">
       <c r="A358" s="2" t="s">
         <v>500</v>
       </c>
@@ -23706,7 +24294,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="359" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:23">
       <c r="A359" s="2" t="s">
         <v>502</v>
       </c>
@@ -23763,7 +24351,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="360" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:23">
       <c r="A360" s="2" t="s">
         <v>503</v>
       </c>
@@ -23820,7 +24408,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="361" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:23">
       <c r="A361" s="2" t="s">
         <v>504</v>
       </c>
@@ -23877,7 +24465,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="362" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:23">
       <c r="A362" s="2" t="s">
         <v>505</v>
       </c>
@@ -23934,7 +24522,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="363" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:23">
       <c r="A363" s="2" t="s">
         <v>506</v>
       </c>
@@ -23991,7 +24579,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="364" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:23">
       <c r="A364" s="2" t="s">
         <v>508</v>
       </c>
@@ -24048,7 +24636,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="365" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:23">
       <c r="A365" s="2" t="s">
         <v>509</v>
       </c>
@@ -24105,7 +24693,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="366" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:23">
       <c r="A366" s="2" t="s">
         <v>510</v>
       </c>
@@ -24162,7 +24750,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="367" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:23">
       <c r="A367" s="2" t="s">
         <v>511</v>
       </c>
@@ -24219,7 +24807,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="368" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:23">
       <c r="A368" s="2" t="s">
         <v>512</v>
       </c>
@@ -24276,7 +24864,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:23">
       <c r="A369" s="2" t="s">
         <v>513</v>
       </c>
@@ -24333,7 +24921,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:23">
       <c r="A370" s="2" t="s">
         <v>515</v>
       </c>
@@ -24390,7 +24978,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:23">
       <c r="A371" s="2" t="s">
         <v>516</v>
       </c>
@@ -24447,7 +25035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:23">
       <c r="A372" s="2" t="s">
         <v>517</v>
       </c>
@@ -24504,7 +25092,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:23">
       <c r="A373" s="2" t="s">
         <v>518</v>
       </c>
@@ -24561,7 +25149,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="374" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:23">
       <c r="A374" s="2" t="s">
         <v>520</v>
       </c>
@@ -24618,7 +25206,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:23" ht="30">
       <c r="A375" s="2" t="s">
         <v>522</v>
       </c>
@@ -24675,7 +25263,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:23" ht="30">
       <c r="A376" s="2" t="s">
         <v>523</v>
       </c>
@@ -24732,7 +25320,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="377" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:23">
       <c r="A377" s="2" t="s">
         <v>524</v>
       </c>
@@ -24789,7 +25377,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="378" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:23">
       <c r="A378" s="2" t="s">
         <v>526</v>
       </c>
@@ -24846,7 +25434,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:23">
       <c r="A379" s="2" t="s">
         <v>528</v>
       </c>
@@ -24903,7 +25491,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:23">
       <c r="A380" s="2" t="s">
         <v>529</v>
       </c>
@@ -24960,7 +25548,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:23">
       <c r="A381" s="2" t="s">
         <v>530</v>
       </c>
@@ -25017,7 +25605,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:23">
       <c r="A382" s="2" t="s">
         <v>531</v>
       </c>
@@ -25074,7 +25662,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="383" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:23">
       <c r="A383" s="2" t="s">
         <v>532</v>
       </c>
@@ -25131,7 +25719,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="384" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:23">
       <c r="A384" s="2" t="s">
         <v>533</v>
       </c>
@@ -25188,7 +25776,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="385" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:23">
       <c r="A385" s="2" t="s">
         <v>534</v>
       </c>
@@ -25245,7 +25833,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="386" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:23">
       <c r="A386" s="2" t="s">
         <v>535</v>
       </c>
@@ -25302,7 +25890,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="387" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:23">
       <c r="A387" s="2" t="s">
         <v>536</v>
       </c>
@@ -25359,7 +25947,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="388" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:23">
       <c r="A388" s="2" t="s">
         <v>537</v>
       </c>
@@ -25416,7 +26004,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="389" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:23">
       <c r="A389" s="2" t="s">
         <v>538</v>
       </c>
@@ -25473,7 +26061,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="390" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:23">
       <c r="A390" s="2" t="s">
         <v>539</v>
       </c>
@@ -25530,7 +26118,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="391" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:23">
       <c r="A391" s="2" t="s">
         <v>541</v>
       </c>
@@ -25587,7 +26175,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="392" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:23">
       <c r="A392" s="2" t="s">
         <v>541</v>
       </c>
@@ -25644,7 +26232,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:23" ht="30">
       <c r="A393" s="2" t="s">
         <v>543</v>
       </c>
@@ -25701,7 +26289,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="394" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:23">
       <c r="A394" s="2" t="s">
         <v>544</v>
       </c>
@@ -25758,7 +26346,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="395" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:23">
       <c r="A395" s="2" t="s">
         <v>546</v>
       </c>
@@ -25815,7 +26403,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="396" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:23">
       <c r="A396" s="2" t="s">
         <v>547</v>
       </c>
@@ -25872,7 +26460,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="397" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:23">
       <c r="A397" s="2" t="s">
         <v>548</v>
       </c>
@@ -25929,7 +26517,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="398" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:23" ht="30">
       <c r="A398" s="2" t="s">
         <v>549</v>
       </c>
@@ -25986,7 +26574,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="399" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:23" ht="30">
       <c r="A399" s="2" t="s">
         <v>550</v>
       </c>
@@ -26043,7 +26631,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="400" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:23">
       <c r="A400" s="2" t="s">
         <v>551</v>
       </c>
@@ -26100,7 +26688,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="401" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:23">
       <c r="A401" s="2" t="s">
         <v>553</v>
       </c>
@@ -26157,7 +26745,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="402" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:23">
       <c r="A402" s="2" t="s">
         <v>554</v>
       </c>
@@ -26214,7 +26802,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="403" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:23">
       <c r="A403" s="2" t="s">
         <v>556</v>
       </c>
@@ -26271,7 +26859,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="404" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:23">
       <c r="A404" s="2" t="s">
         <v>557</v>
       </c>
@@ -26328,7 +26916,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="405" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:23">
       <c r="A405" s="2" t="s">
         <v>558</v>
       </c>
@@ -26385,7 +26973,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="406" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:23">
       <c r="A406" s="2" t="s">
         <v>559</v>
       </c>
@@ -26442,7 +27030,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="407" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:23" ht="30">
       <c r="A407" s="2" t="s">
         <v>560</v>
       </c>
@@ -26499,7 +27087,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="408" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:23" ht="30">
       <c r="A408" s="2" t="s">
         <v>562</v>
       </c>
@@ -26556,7 +27144,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="409" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:23" ht="30">
       <c r="A409" s="2" t="s">
         <v>563</v>
       </c>
@@ -26613,7 +27201,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="410" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:23" ht="30">
       <c r="A410" s="2" t="s">
         <v>564</v>
       </c>
@@ -26670,7 +27258,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="411" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:23" ht="30">
       <c r="A411" s="2" t="s">
         <v>565</v>
       </c>
@@ -26727,7 +27315,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="412" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:23">
       <c r="A412" s="2" t="s">
         <v>483</v>
       </c>
@@ -26784,7 +27372,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="413" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:23">
       <c r="A413" s="2" t="s">
         <v>246</v>
       </c>
@@ -26841,7 +27429,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="414" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:23">
       <c r="A414" s="2" t="s">
         <v>566</v>
       </c>
@@ -26898,7 +27486,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="415" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:23">
       <c r="A415" s="2" t="s">
         <v>567</v>
       </c>
@@ -26955,7 +27543,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="416" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:23" ht="30">
       <c r="A416" s="2" t="s">
         <v>568</v>
       </c>
@@ -27012,7 +27600,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="417" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:23">
       <c r="A417" s="2" t="s">
         <v>569</v>
       </c>
@@ -27069,7 +27657,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="418" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:23" ht="30">
       <c r="A418" s="2" t="s">
         <v>571</v>
       </c>
@@ -27126,7 +27714,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="419" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:23" ht="30">
       <c r="A419" s="2" t="s">
         <v>572</v>
       </c>
@@ -27183,7 +27771,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="420" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:23" ht="30">
       <c r="A420" s="2" t="s">
         <v>573</v>
       </c>
@@ -27240,7 +27828,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="421" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:23" ht="30">
       <c r="A421" s="2" t="s">
         <v>253</v>
       </c>
@@ -27297,7 +27885,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="422" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:23">
       <c r="A422" s="2" t="s">
         <v>574</v>
       </c>
@@ -27354,7 +27942,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="423" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:23" ht="30">
       <c r="A423" s="2" t="s">
         <v>192</v>
       </c>
@@ -27411,7 +27999,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="424" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:23" ht="30">
       <c r="A424" s="2" t="s">
         <v>577</v>
       </c>
@@ -27468,7 +28056,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="425" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:23">
       <c r="A425" s="2" t="s">
         <v>578</v>
       </c>
@@ -27525,7 +28113,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="426" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:23">
       <c r="A426" s="2" t="s">
         <v>579</v>
       </c>
@@ -27582,7 +28170,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="427" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:23" ht="30">
       <c r="A427" s="2" t="s">
         <v>580</v>
       </c>
@@ -27639,7 +28227,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="428" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:23" ht="30">
       <c r="A428" s="2" t="s">
         <v>581</v>
       </c>
@@ -27696,7 +28284,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="429" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:23">
       <c r="A429" s="2" t="s">
         <v>582</v>
       </c>
@@ -27753,7 +28341,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="430" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:23">
       <c r="A430" s="2" t="s">
         <v>583</v>
       </c>
@@ -27810,7 +28398,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="431" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:23">
       <c r="A431" s="2" t="s">
         <v>584</v>
       </c>
@@ -27867,7 +28455,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="432" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:23">
       <c r="A432" s="2" t="s">
         <v>585</v>
       </c>
@@ -27924,7 +28512,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="433" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:23">
       <c r="A433" s="2" t="s">
         <v>586</v>
       </c>
@@ -27981,7 +28569,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="434" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:23">
       <c r="A434" s="2" t="s">
         <v>587</v>
       </c>
@@ -28038,7 +28626,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="435" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:23">
       <c r="A435" s="2" t="s">
         <v>588</v>
       </c>
@@ -28095,7 +28683,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="436" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:23" ht="30">
       <c r="A436" s="2" t="s">
         <v>589</v>
       </c>
@@ -28152,7 +28740,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="437" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:23">
       <c r="A437" s="2" t="s">
         <v>590</v>
       </c>
@@ -28209,7 +28797,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="438" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:23">
       <c r="A438" s="2" t="s">
         <v>592</v>
       </c>
@@ -28266,7 +28854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="439" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:23">
       <c r="A439" s="2" t="s">
         <v>594</v>
       </c>
@@ -28323,7 +28911,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="440" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:23">
       <c r="A440" s="2" t="s">
         <v>595</v>
       </c>
@@ -28380,7 +28968,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="441" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:23">
       <c r="A441" s="2" t="s">
         <v>596</v>
       </c>
@@ -28437,7 +29025,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="442" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:23">
       <c r="A442" s="2" t="s">
         <v>597</v>
       </c>
@@ -28494,7 +29082,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="443" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:23" ht="30">
       <c r="A443" s="2" t="s">
         <v>599</v>
       </c>
@@ -28551,7 +29139,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="444" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:23">
       <c r="A444" s="2" t="s">
         <v>600</v>
       </c>
@@ -28608,7 +29196,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="445" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:23">
       <c r="A445" s="2" t="s">
         <v>601</v>
       </c>
@@ -28665,7 +29253,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="446" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:23">
       <c r="A446" s="2" t="s">
         <v>602</v>
       </c>
@@ -28722,7 +29310,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="447" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:23">
       <c r="A447" s="2" t="s">
         <v>603</v>
       </c>
@@ -28779,7 +29367,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="448" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:23">
       <c r="A448" s="2" t="s">
         <v>604</v>
       </c>
@@ -28836,7 +29424,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="449" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:23">
       <c r="A449" s="2" t="s">
         <v>605</v>
       </c>
@@ -28893,7 +29481,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="450" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:23">
       <c r="A450" s="2" t="s">
         <v>606</v>
       </c>
@@ -28950,7 +29538,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="451" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:23">
       <c r="A451" s="2" t="s">
         <v>607</v>
       </c>
@@ -29007,7 +29595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="452" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:23" ht="30">
       <c r="A452" s="2" t="s">
         <v>608</v>
       </c>
@@ -29064,7 +29652,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="453" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:23">
       <c r="A453" s="2" t="s">
         <v>610</v>
       </c>
@@ -29121,7 +29709,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="454" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:23">
       <c r="A454" s="2" t="s">
         <v>611</v>
       </c>
@@ -29178,7 +29766,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="455" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:23" ht="30">
       <c r="A455" s="2" t="s">
         <v>613</v>
       </c>
@@ -29235,7 +29823,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="456" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:23">
       <c r="A456" s="2" t="s">
         <v>615</v>
       </c>
@@ -29292,7 +29880,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="457" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:23">
       <c r="A457" s="2" t="s">
         <v>617</v>
       </c>
@@ -29349,7 +29937,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="458" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:23" ht="30">
       <c r="A458" s="2" t="s">
         <v>618</v>
       </c>
@@ -29406,7 +29994,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="459" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:23">
       <c r="A459" s="2" t="s">
         <v>620</v>
       </c>
@@ -29463,7 +30051,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="460" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:23">
       <c r="A460" s="2" t="s">
         <v>621</v>
       </c>
@@ -29520,7 +30108,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="461" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:23">
       <c r="A461" s="2" t="s">
         <v>622</v>
       </c>
@@ -29577,7 +30165,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="462" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:23">
       <c r="A462" s="2" t="s">
         <v>623</v>
       </c>
@@ -29634,7 +30222,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="463" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:23">
       <c r="A463" s="2" t="s">
         <v>624</v>
       </c>
@@ -29691,7 +30279,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="464" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:23">
       <c r="A464" s="2" t="s">
         <v>625</v>
       </c>
@@ -29748,7 +30336,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="465" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:23" ht="30">
       <c r="A465" s="2" t="s">
         <v>626</v>
       </c>
@@ -29805,7 +30393,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="466" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:23" ht="30">
       <c r="A466" s="2" t="s">
         <v>627</v>
       </c>
@@ -29862,7 +30450,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="467" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:23" ht="30">
       <c r="A467" s="2" t="s">
         <v>628</v>
       </c>
@@ -29919,7 +30507,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="468" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:23">
       <c r="A468" s="2" t="s">
         <v>629</v>
       </c>
@@ -29976,7 +30564,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="469" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:23">
       <c r="A469" s="2" t="s">
         <v>630</v>
       </c>
@@ -30033,7 +30621,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="470" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:23">
       <c r="A470" s="2" t="s">
         <v>631</v>
       </c>
@@ -30090,7 +30678,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="471" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:23">
       <c r="A471" s="2" t="s">
         <v>632</v>
       </c>
@@ -30147,7 +30735,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="472" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:23">
       <c r="A472" s="2" t="s">
         <v>633</v>
       </c>
@@ -30204,7 +30792,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="473" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:23">
       <c r="A473" s="2" t="s">
         <v>634</v>
       </c>
@@ -30261,7 +30849,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="474" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:23" ht="30">
       <c r="A474" s="2" t="s">
         <v>635</v>
       </c>
@@ -30318,7 +30906,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="475" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:23" ht="30">
       <c r="A475" s="2" t="s">
         <v>572</v>
       </c>
@@ -30375,7 +30963,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="476" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:23">
       <c r="A476" s="2" t="s">
         <v>572</v>
       </c>
@@ -30432,7 +31020,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="477" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:23" ht="30">
       <c r="A477" s="2" t="s">
         <v>638</v>
       </c>
@@ -30489,7 +31077,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="478" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:23" ht="30">
       <c r="A478" s="2" t="s">
         <v>639</v>
       </c>
@@ -30546,7 +31134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="479" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:23" ht="30">
       <c r="A479" s="2" t="s">
         <v>640</v>
       </c>
@@ -30603,7 +31191,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="480" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:23" ht="30">
       <c r="A480" s="2" t="s">
         <v>641</v>
       </c>
@@ -30660,7 +31248,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="481" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:23" ht="30">
       <c r="A481" s="2" t="s">
         <v>642</v>
       </c>
@@ -30717,7 +31305,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="482" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:23">
       <c r="A482" s="2" t="s">
         <v>254</v>
       </c>
@@ -30774,7 +31362,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="483" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:23">
       <c r="A483" s="2" t="s">
         <v>644</v>
       </c>
@@ -30831,7 +31419,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="484" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:23">
       <c r="A484" s="2" t="s">
         <v>646</v>
       </c>
@@ -30888,7 +31476,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="485" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:23" ht="30">
       <c r="A485" s="2" t="s">
         <v>647</v>
       </c>
@@ -30945,7 +31533,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="486" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:23">
       <c r="A486" s="2" t="s">
         <v>649</v>
       </c>
@@ -31002,7 +31590,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="487" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:23">
       <c r="A487" s="2" t="s">
         <v>650</v>
       </c>
@@ -31059,7 +31647,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="488" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:23">
       <c r="A488" s="2" t="s">
         <v>651</v>
       </c>
@@ -31116,7 +31704,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="489" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:23">
       <c r="A489" s="2" t="s">
         <v>652</v>
       </c>
@@ -31173,7 +31761,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="490" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:23">
       <c r="A490" s="2" t="s">
         <v>654</v>
       </c>
@@ -31230,7 +31818,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="491" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:23">
       <c r="A491" s="2" t="s">
         <v>656</v>
       </c>
@@ -31287,7 +31875,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="492" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:23">
       <c r="A492" s="2" t="s">
         <v>658</v>
       </c>
@@ -31344,7 +31932,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="493" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:23">
       <c r="A493" s="2" t="s">
         <v>659</v>
       </c>
@@ -31401,7 +31989,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="494" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:23">
       <c r="A494" s="2" t="s">
         <v>661</v>
       </c>
@@ -31458,7 +32046,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="495" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:23" ht="30">
       <c r="A495" s="2" t="s">
         <v>662</v>
       </c>
@@ -31515,7 +32103,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="496" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:23" ht="30">
       <c r="A496" s="2" t="s">
         <v>663</v>
       </c>
@@ -31572,7 +32160,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="497" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:23">
       <c r="A497" s="2" t="s">
         <v>664</v>
       </c>
@@ -31629,7 +32217,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="498" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:23">
       <c r="A498" s="2" t="s">
         <v>665</v>
       </c>
@@ -31686,7 +32274,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="499" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:23">
       <c r="A499" s="2" t="s">
         <v>666</v>
       </c>
@@ -31743,7 +32331,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="500" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:23">
       <c r="A500" s="2" t="s">
         <v>667</v>
       </c>
@@ -31800,7 +32388,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="501" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:23">
       <c r="A501" s="2" t="s">
         <v>668</v>
       </c>
@@ -31857,7 +32445,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="502" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:23">
       <c r="A502" s="2" t="s">
         <v>669</v>
       </c>
@@ -31914,7 +32502,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="503" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:23">
       <c r="A503" s="2" t="s">
         <v>670</v>
       </c>
@@ -31971,7 +32559,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="504" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:23">
       <c r="A504" s="2" t="s">
         <v>671</v>
       </c>
@@ -32028,7 +32616,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="505" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:23">
       <c r="A505" s="2" t="s">
         <v>672</v>
       </c>
@@ -32085,7 +32673,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="506" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:23">
       <c r="A506" s="2" t="s">
         <v>673</v>
       </c>
@@ -32142,7 +32730,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="507" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:23">
       <c r="A507" s="2" t="s">
         <v>674</v>
       </c>
@@ -32199,7 +32787,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="508" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:23">
       <c r="A508" s="2" t="s">
         <v>675</v>
       </c>
@@ -32256,7 +32844,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="509" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:23">
       <c r="A509" s="2" t="s">
         <v>676</v>
       </c>
@@ -32313,7 +32901,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="510" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:23">
       <c r="A510" s="2" t="s">
         <v>677</v>
       </c>
@@ -32370,7 +32958,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="511" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:23">
       <c r="A511" s="2" t="s">
         <v>678</v>
       </c>
@@ -32427,7 +33015,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="512" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:23">
       <c r="A512" s="2" t="s">
         <v>679</v>
       </c>
@@ -32484,7 +33072,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="513" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:23">
       <c r="A513" s="2" t="s">
         <v>680</v>
       </c>
@@ -32541,7 +33129,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="514" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:23">
       <c r="A514" s="2" t="s">
         <v>681</v>
       </c>
@@ -32598,7 +33186,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="515" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:23">
       <c r="A515" s="2" t="s">
         <v>682</v>
       </c>
@@ -32655,7 +33243,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="516" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:23">
       <c r="A516" s="2" t="s">
         <v>683</v>
       </c>
@@ -32712,7 +33300,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="517" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:23">
       <c r="A517" s="2" t="s">
         <v>684</v>
       </c>
@@ -32769,7 +33357,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="518" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:23">
       <c r="A518" s="2" t="s">
         <v>685</v>
       </c>
@@ -32826,7 +33414,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="519" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:23">
       <c r="A519" s="2" t="s">
         <v>686</v>
       </c>
@@ -32883,7 +33471,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="520" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:23" ht="30">
       <c r="A520" s="2" t="s">
         <v>687</v>
       </c>
@@ -32940,7 +33528,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="521" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:23">
       <c r="A521" s="2" t="s">
         <v>688</v>
       </c>
@@ -32997,7 +33585,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="522" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:23" ht="30">
       <c r="A522" s="2" t="s">
         <v>689</v>
       </c>
@@ -33054,7 +33642,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="523" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:23">
       <c r="A523" s="2" t="s">
         <v>690</v>
       </c>
@@ -33111,7 +33699,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="524" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:23" ht="30">
       <c r="A524" s="2" t="s">
         <v>691</v>
       </c>
@@ -33168,7 +33756,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="525" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:23">
       <c r="A525" s="2" t="s">
         <v>692</v>
       </c>
@@ -33225,7 +33813,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="526" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:23">
       <c r="A526" s="2" t="s">
         <v>693</v>
       </c>
@@ -33282,7 +33870,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="527" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:23">
       <c r="A527" s="2" t="s">
         <v>694</v>
       </c>
@@ -33339,7 +33927,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="528" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:23">
       <c r="A528" s="2" t="s">
         <v>695</v>
       </c>
@@ -33396,7 +33984,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="529" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:23">
       <c r="A529" s="2" t="s">
         <v>696</v>
       </c>
@@ -33453,7 +34041,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="530" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:23">
       <c r="A530" s="2" t="s">
         <v>697</v>
       </c>
@@ -33510,7 +34098,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="531" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:23" ht="30">
       <c r="A531" s="2" t="s">
         <v>698</v>
       </c>
@@ -33567,7 +34155,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="532" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:23">
       <c r="A532" s="2" t="s">
         <v>700</v>
       </c>
@@ -33624,7 +34212,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="533" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:23">
       <c r="A533" s="2" t="s">
         <v>702</v>
       </c>
@@ -33681,7 +34269,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="534" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:23">
       <c r="A534" s="2" t="s">
         <v>704</v>
       </c>
@@ -33738,7 +34326,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="535" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:23">
       <c r="A535" s="2"/>
       <c r="B535" s="2">
         <v>0</v>
@@ -33793,7 +34381,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="536" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:23">
       <c r="A536" s="2" t="s">
         <v>573</v>
       </c>
@@ -33850,7 +34438,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="537" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:23" ht="30">
       <c r="A537" s="2" t="s">
         <v>705</v>
       </c>
@@ -33907,7 +34495,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="538" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:23" ht="30">
       <c r="A538" s="2" t="s">
         <v>706</v>
       </c>
@@ -33964,7 +34552,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="539" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:23" ht="30">
       <c r="A539" s="2" t="s">
         <v>707</v>
       </c>
@@ -34021,7 +34609,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="540" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:23" ht="30">
       <c r="A540" s="2" t="s">
         <v>708</v>
       </c>
@@ -34078,7 +34666,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="541" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:23" ht="30">
       <c r="A541" s="2" t="s">
         <v>386</v>
       </c>
@@ -34135,7 +34723,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="542" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:23" ht="30">
       <c r="A542" s="2" t="s">
         <v>709</v>
       </c>
@@ -34192,7 +34780,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="543" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:23" ht="30">
       <c r="A543" s="2" t="s">
         <v>710</v>
       </c>
@@ -34249,7 +34837,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="544" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:23">
       <c r="A544" s="2" t="s">
         <v>711</v>
       </c>
@@ -34306,7 +34894,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="545" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:23">
       <c r="A545" s="2" t="s">
         <v>712</v>
       </c>
@@ -34363,7 +34951,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="546" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:23">
       <c r="A546" s="2" t="s">
         <v>713</v>
       </c>
@@ -34420,7 +35008,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="547" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:23">
       <c r="A547" s="2" t="s">
         <v>714</v>
       </c>
@@ -34477,7 +35065,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="548" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:23">
       <c r="A548" s="2" t="s">
         <v>715</v>
       </c>
@@ -34534,7 +35122,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="549" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:23">
       <c r="A549" s="2" t="s">
         <v>716</v>
       </c>
@@ -34591,7 +35179,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="550" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:23">
       <c r="A550" s="2" t="s">
         <v>717</v>
       </c>
@@ -34648,7 +35236,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="551" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:23">
       <c r="A551" s="2" t="s">
         <v>718</v>
       </c>
@@ -34705,7 +35293,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="552" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:23">
       <c r="A552" s="2" t="s">
         <v>719</v>
       </c>
@@ -34762,7 +35350,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="553" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:23" ht="30">
       <c r="A553" s="2" t="s">
         <v>721</v>
       </c>
@@ -34819,7 +35407,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="554" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:23">
       <c r="A554" s="2" t="s">
         <v>722</v>
       </c>
@@ -34876,7 +35464,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="555" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:23">
       <c r="A555" s="2" t="s">
         <v>724</v>
       </c>
@@ -34933,7 +35521,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="556" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:23">
       <c r="A556" s="2" t="s">
         <v>725</v>
       </c>
@@ -34990,7 +35578,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="557" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:23">
       <c r="A557" s="2" t="s">
         <v>726</v>
       </c>
@@ -35047,7 +35635,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="558" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:23">
       <c r="A558" s="2" t="s">
         <v>727</v>
       </c>
@@ -35104,7 +35692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="559" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:23">
       <c r="A559" s="2" t="s">
         <v>728</v>
       </c>
@@ -35161,7 +35749,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="560" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:23">
       <c r="A560" s="2" t="s">
         <v>729</v>
       </c>
@@ -35218,7 +35806,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="561" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:23">
       <c r="A561" s="2" t="s">
         <v>730</v>
       </c>
@@ -35275,7 +35863,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="562" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:23">
       <c r="A562" s="2" t="s">
         <v>731</v>
       </c>
@@ -35332,7 +35920,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="563" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:23" ht="30">
       <c r="A563" s="2" t="s">
         <v>733</v>
       </c>
@@ -35389,7 +35977,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="564" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:23" ht="30">
       <c r="A564" s="2" t="s">
         <v>735</v>
       </c>
@@ -35446,7 +36034,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="565" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:23" ht="30">
       <c r="A565" s="2" t="s">
         <v>737</v>
       </c>
@@ -35503,7 +36091,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="566" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:23">
       <c r="A566" s="2" t="s">
         <v>739</v>
       </c>
@@ -35560,7 +36148,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="567" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:23">
       <c r="A567" s="2" t="s">
         <v>740</v>
       </c>
@@ -35617,7 +36205,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="568" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:23">
       <c r="A568" s="2" t="s">
         <v>741</v>
       </c>
@@ -35674,7 +36262,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="569" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:23">
       <c r="A569" s="2" t="s">
         <v>742</v>
       </c>
@@ -35731,7 +36319,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="570" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:23" ht="30">
       <c r="A570" s="2" t="s">
         <v>743</v>
       </c>
@@ -35788,7 +36376,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="571" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:23">
       <c r="A571" s="2" t="s">
         <v>744</v>
       </c>
@@ -35845,7 +36433,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="572" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:23" ht="30">
       <c r="A572" s="2" t="s">
         <v>745</v>
       </c>
@@ -35902,7 +36490,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="573" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:23">
       <c r="A573" s="2" t="s">
         <v>746</v>
       </c>
@@ -35959,7 +36547,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="574" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:23">
       <c r="A574" s="2" t="s">
         <v>747</v>
       </c>
@@ -36016,7 +36604,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="575" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:23">
       <c r="A575" s="2" t="s">
         <v>748</v>
       </c>
@@ -36073,7 +36661,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="576" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:23">
       <c r="A576" s="2" t="s">
         <v>749</v>
       </c>
@@ -36130,7 +36718,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="577" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:23">
       <c r="A577" s="2" t="s">
         <v>750</v>
       </c>
@@ -36187,7 +36775,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="578" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:23">
       <c r="A578" s="2" t="s">
         <v>751</v>
       </c>
@@ -36244,7 +36832,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="579" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:23">
       <c r="A579" s="2" t="s">
         <v>752</v>
       </c>
@@ -36301,7 +36889,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="580" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:23">
       <c r="A580" s="2" t="s">
         <v>753</v>
       </c>
@@ -36358,7 +36946,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="581" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:23" ht="30">
       <c r="A581" s="2" t="s">
         <v>755</v>
       </c>
@@ -36415,7 +37003,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="582" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:23" ht="30">
       <c r="A582" s="2" t="s">
         <v>756</v>
       </c>
@@ -36472,7 +37060,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="583" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:23" ht="30">
       <c r="A583" s="2" t="s">
         <v>495</v>
       </c>
@@ -36529,7 +37117,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="584" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:23" ht="30">
       <c r="A584" s="2" t="s">
         <v>757</v>
       </c>
@@ -36586,7 +37174,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="585" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:23" ht="30">
       <c r="A585" s="2" t="s">
         <v>759</v>
       </c>
@@ -36643,7 +37231,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="586" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:23">
       <c r="A586" s="2" t="s">
         <v>760</v>
       </c>
@@ -36700,7 +37288,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="587" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:23">
       <c r="A587" s="2" t="s">
         <v>761</v>
       </c>
@@ -36757,7 +37345,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="588" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:23">
       <c r="A588" s="2" t="s">
         <v>762</v>
       </c>
@@ -36814,7 +37402,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="589" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:23">
       <c r="A589" s="2" t="s">
         <v>764</v>
       </c>
@@ -36871,7 +37459,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="590" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:23">
       <c r="A590" s="2" t="s">
         <v>765</v>
       </c>
@@ -36928,7 +37516,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="591" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:23">
       <c r="A591" s="2" t="s">
         <v>766</v>
       </c>
@@ -36985,7 +37573,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="592" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:23" ht="30">
       <c r="A592" s="2" t="s">
         <v>767</v>
       </c>
@@ -37042,7 +37630,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="593" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:23" ht="30">
       <c r="A593" s="2" t="s">
         <v>768</v>
       </c>
@@ -37099,7 +37687,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="594" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:23">
       <c r="A594" s="2" t="s">
         <v>769</v>
       </c>
@@ -37156,7 +37744,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="595" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:23">
       <c r="A595" s="2" t="s">
         <v>770</v>
       </c>
@@ -37213,7 +37801,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="596" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:23">
       <c r="A596" s="2" t="s">
         <v>771</v>
       </c>
@@ -37270,7 +37858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="597" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:23">
       <c r="A597" s="2" t="s">
         <v>772</v>
       </c>
@@ -37327,7 +37915,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="598" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:23" ht="30">
       <c r="A598" s="2" t="s">
         <v>773</v>
       </c>
@@ -37384,7 +37972,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="599" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:23">
       <c r="A599" s="2" t="s">
         <v>774</v>
       </c>
@@ -37441,7 +38029,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="600" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:23">
       <c r="A600" s="2" t="s">
         <v>775</v>
       </c>
@@ -37498,7 +38086,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="601" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:23">
       <c r="A601" s="2" t="s">
         <v>777</v>
       </c>
@@ -37555,7 +38143,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="602" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:23">
       <c r="A602" s="2" t="s">
         <v>779</v>
       </c>
@@ -37612,7 +38200,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="603" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:23" ht="30">
       <c r="A603" s="2" t="s">
         <v>780</v>
       </c>
@@ -37669,7 +38257,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="604" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:23" ht="30">
       <c r="A604" s="2" t="s">
         <v>781</v>
       </c>
@@ -37726,7 +38314,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="605" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:23">
       <c r="A605" s="2" t="s">
         <v>782</v>
       </c>
@@ -37783,7 +38371,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="606" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:23">
       <c r="A606" s="2" t="s">
         <v>783</v>
       </c>
@@ -37840,7 +38428,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="607" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:23">
       <c r="A607" s="2" t="s">
         <v>784</v>
       </c>
@@ -37897,7 +38485,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="608" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:23">
       <c r="A608" s="2" t="s">
         <v>785</v>
       </c>
@@ -37954,7 +38542,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="609" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:23">
       <c r="A609" s="2" t="s">
         <v>786</v>
       </c>
@@ -38011,7 +38599,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="610" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:23">
       <c r="A610" s="2" t="s">
         <v>787</v>
       </c>
@@ -38068,7 +38656,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="611" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:23">
       <c r="A611" s="2" t="s">
         <v>788</v>
       </c>
@@ -38125,7 +38713,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="612" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:23">
       <c r="A612" s="2" t="s">
         <v>790</v>
       </c>
@@ -38182,7 +38770,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="613" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:23">
       <c r="A613" s="2" t="s">
         <v>791</v>
       </c>
@@ -38239,7 +38827,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="614" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:23" ht="30">
       <c r="A614" s="2" t="s">
         <v>688</v>
       </c>
@@ -38296,7 +38884,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="615" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:23" ht="30">
       <c r="A615" s="2" t="s">
         <v>792</v>
       </c>
@@ -38353,7 +38941,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="616" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:23" ht="30">
       <c r="A616" s="2" t="s">
         <v>794</v>
       </c>
@@ -38410,7 +38998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="617" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:23" ht="30">
       <c r="A617" s="2" t="s">
         <v>794</v>
       </c>
@@ -38467,7 +39055,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="618" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:23" ht="30">
       <c r="A618" s="2" t="s">
         <v>795</v>
       </c>
@@ -38524,7 +39112,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="619" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:23">
       <c r="A619" s="2" t="s">
         <v>797</v>
       </c>
@@ -38581,7 +39169,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="620" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:23">
       <c r="A620" s="2" t="s">
         <v>798</v>
       </c>
@@ -38638,7 +39226,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="621" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:23" ht="30">
       <c r="A621" s="2" t="s">
         <v>800</v>
       </c>
@@ -38695,7 +39283,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="622" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:23">
       <c r="A622" s="2" t="s">
         <v>802</v>
       </c>
@@ -38752,7 +39340,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="623" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:23">
       <c r="A623" s="2"/>
       <c r="B623" s="2">
         <v>0</v>
@@ -38807,7 +39395,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="624" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:23" ht="30">
       <c r="A624" s="2" t="s">
         <v>64</v>
       </c>
@@ -38864,7 +39452,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="625" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:23">
       <c r="A625" s="2" t="s">
         <v>804</v>
       </c>
@@ -38921,7 +39509,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="626" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:23" ht="30">
       <c r="A626" s="2" t="s">
         <v>806</v>
       </c>
@@ -38978,7 +39566,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="627" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:23">
       <c r="A627" s="2" t="s">
         <v>574</v>
       </c>
@@ -39035,7 +39623,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="628" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:23" ht="30">
       <c r="A628" s="2" t="s">
         <v>71</v>
       </c>
@@ -39092,7 +39680,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="629" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:23" ht="30">
       <c r="A629" s="2" t="s">
         <v>191</v>
       </c>
@@ -39149,7 +39737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="630" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:23" ht="30">
       <c r="A630" s="2" t="s">
         <v>807</v>
       </c>
@@ -39206,7 +39794,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="631" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:23">
       <c r="A631" s="2" t="s">
         <v>808</v>
       </c>
@@ -39263,7 +39851,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="632" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:23">
       <c r="A632" s="2" t="s">
         <v>810</v>
       </c>
@@ -39320,7 +39908,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="633" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:23" ht="30">
       <c r="A633" s="2" t="s">
         <v>811</v>
       </c>
@@ -39377,7 +39965,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="634" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:23" ht="45">
       <c r="A634" s="2" t="s">
         <v>813</v>
       </c>
@@ -39434,7 +40022,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="635" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:23">
       <c r="A635" s="2" t="s">
         <v>815</v>
       </c>
@@ -39491,7 +40079,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="636" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:23">
       <c r="A636" s="2" t="s">
         <v>816</v>
       </c>
@@ -39548,7 +40136,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="637" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:23">
       <c r="A637" s="2" t="s">
         <v>818</v>
       </c>
@@ -39605,7 +40193,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="638" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:23" ht="30">
       <c r="A638" s="2" t="s">
         <v>820</v>
       </c>
@@ -39662,7 +40250,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="639" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:23">
       <c r="A639" s="2" t="s">
         <v>822</v>
       </c>
@@ -39719,7 +40307,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="640" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:23">
       <c r="A640" s="2" t="s">
         <v>823</v>
       </c>
@@ -39776,7 +40364,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="641" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:23">
       <c r="A641" s="2" t="s">
         <v>824</v>
       </c>
@@ -39833,7 +40421,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="642" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:23">
       <c r="A642" s="2" t="s">
         <v>825</v>
       </c>
@@ -39890,7 +40478,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="643" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:23">
       <c r="A643" s="2" t="s">
         <v>826</v>
       </c>
@@ -39947,7 +40535,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="644" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:23">
       <c r="A644" s="2" t="s">
         <v>827</v>
       </c>
@@ -40004,7 +40592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="645" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:23">
       <c r="A645" s="2" t="s">
         <v>828</v>
       </c>
@@ -40061,7 +40649,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="646" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:23" ht="30">
       <c r="A646" s="2" t="s">
         <v>829</v>
       </c>
@@ -40118,7 +40706,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="647" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:23" ht="30">
       <c r="A647" s="2" t="s">
         <v>830</v>
       </c>
@@ -40175,7 +40763,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="648" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:23">
       <c r="A648" s="2" t="s">
         <v>434</v>
       </c>
@@ -40232,7 +40820,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="649" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:23" ht="30">
       <c r="A649" s="2" t="s">
         <v>832</v>
       </c>
@@ -40289,7 +40877,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="650" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:23" ht="30">
       <c r="A650" s="2" t="s">
         <v>833</v>
       </c>
@@ -40346,7 +40934,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="651" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:23">
       <c r="A651" s="2" t="s">
         <v>834</v>
       </c>
@@ -40403,7 +40991,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="652" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:23">
       <c r="A652" s="2" t="s">
         <v>836</v>
       </c>
@@ -40460,7 +41048,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="653" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:23">
       <c r="A653" s="2" t="s">
         <v>837</v>
       </c>
@@ -40517,7 +41105,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="654" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:23">
       <c r="A654" s="2" t="s">
         <v>838</v>
       </c>
@@ -40574,7 +41162,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="655" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:23">
       <c r="A655" s="2" t="s">
         <v>839</v>
       </c>
@@ -40631,7 +41219,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="656" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:23">
       <c r="A656" s="2" t="s">
         <v>840</v>
       </c>
@@ -40688,7 +41276,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="657" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:23">
       <c r="A657" s="2" t="s">
         <v>841</v>
       </c>
@@ -40745,7 +41333,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="658" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:23">
       <c r="A658" s="2" t="s">
         <v>842</v>
       </c>
@@ -40802,7 +41390,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="659" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:23">
       <c r="A659" s="2" t="s">
         <v>843</v>
       </c>
@@ -40859,7 +41447,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="660" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:23">
       <c r="A660" s="2" t="s">
         <v>844</v>
       </c>
@@ -40916,7 +41504,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="661" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:23" ht="30">
       <c r="A661" s="2" t="s">
         <v>845</v>
       </c>
@@ -40973,7 +41561,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="662" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:23">
       <c r="A662" s="2" t="s">
         <v>847</v>
       </c>
@@ -41030,7 +41618,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="663" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:23">
       <c r="A663" s="2" t="s">
         <v>849</v>
       </c>
@@ -41087,7 +41675,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="664" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:23" ht="30">
       <c r="A664" s="2" t="s">
         <v>850</v>
       </c>
@@ -41144,7 +41732,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="665" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:23" ht="30">
       <c r="A665" s="2" t="s">
         <v>852</v>
       </c>
@@ -41201,7 +41789,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="666" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:23">
       <c r="A666" s="2" t="s">
         <v>853</v>
       </c>
@@ -41258,7 +41846,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="667" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:23">
       <c r="A667" s="2" t="s">
         <v>855</v>
       </c>
@@ -41315,7 +41903,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="668" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:23">
       <c r="A668" s="2" t="s">
         <v>856</v>
       </c>
@@ -41372,7 +41960,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="669" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:23">
       <c r="A669" s="2" t="s">
         <v>857</v>
       </c>
@@ -41429,7 +42017,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="670" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:23">
       <c r="A670" s="2" t="s">
         <v>858</v>
       </c>
@@ -41486,7 +42074,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="671" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:23">
       <c r="A671" s="2" t="s">
         <v>859</v>
       </c>
@@ -41543,7 +42131,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="672" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:23" ht="30">
       <c r="A672" s="2" t="s">
         <v>860</v>
       </c>
@@ -41600,7 +42188,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="673" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:23" ht="30">
       <c r="A673" s="2" t="s">
         <v>862</v>
       </c>
@@ -41657,7 +42245,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="674" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:23" ht="30">
       <c r="A674" s="2" t="s">
         <v>864</v>
       </c>
@@ -41714,7 +42302,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="675" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:23" ht="30">
       <c r="A675" s="2" t="s">
         <v>865</v>
       </c>
@@ -41771,7 +42359,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="676" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:23" ht="30">
       <c r="A676" s="2" t="s">
         <v>866</v>
       </c>
@@ -41828,7 +42416,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="677" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:23" ht="30">
       <c r="A677" s="2" t="s">
         <v>867</v>
       </c>
@@ -41885,7 +42473,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="678" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:23" ht="30">
       <c r="A678" s="2" t="s">
         <v>869</v>
       </c>
@@ -41942,7 +42530,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="679" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:23" ht="30">
       <c r="A679" s="2" t="s">
         <v>871</v>
       </c>
@@ -41999,7 +42587,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="680" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:23" ht="30">
       <c r="A680" s="2" t="s">
         <v>254</v>
       </c>
@@ -42056,7 +42644,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="681" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:23">
       <c r="A681" s="2" t="s">
         <v>872</v>
       </c>
@@ -42113,7 +42701,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="682" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:23">
       <c r="A682" s="2" t="s">
         <v>873</v>
       </c>
@@ -42170,7 +42758,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="683" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:23" ht="30">
       <c r="A683" s="2" t="s">
         <v>875</v>
       </c>
@@ -42227,7 +42815,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="684" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:23" ht="30">
       <c r="A684" s="2" t="s">
         <v>876</v>
       </c>
@@ -42284,7 +42872,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="685" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:23">
       <c r="A685" s="2" t="s">
         <v>877</v>
       </c>
@@ -42341,7 +42929,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="686" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:23">
       <c r="A686" s="2" t="s">
         <v>879</v>
       </c>
@@ -42398,7 +42986,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="687" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:23">
       <c r="A687" s="2" t="s">
         <v>881</v>
       </c>
@@ -42455,7 +43043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="688" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:23">
       <c r="A688" s="2" t="s">
         <v>882</v>
       </c>
@@ -42512,7 +43100,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="689" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:23">
       <c r="A689" s="2" t="s">
         <v>883</v>
       </c>
@@ -42569,7 +43157,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="690" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:23" ht="30">
       <c r="A690" s="2" t="s">
         <v>884</v>
       </c>
@@ -42626,7 +43214,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="691" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:23">
       <c r="A691" s="2" t="s">
         <v>885</v>
       </c>
@@ -42683,7 +43271,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="692" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:23">
       <c r="A692" s="2" t="s">
         <v>887</v>
       </c>
@@ -42740,7 +43328,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="693" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:23">
       <c r="A693" s="2" t="s">
         <v>888</v>
       </c>
@@ -42797,7 +43385,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="694" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:23">
       <c r="A694" s="2" t="s">
         <v>889</v>
       </c>
@@ -42854,7 +43442,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="695" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:23">
       <c r="A695" s="2" t="s">
         <v>890</v>
       </c>
@@ -42911,7 +43499,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="696" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:23">
       <c r="A696" s="2" t="s">
         <v>891</v>
       </c>
@@ -42968,7 +43556,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="697" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:23" ht="30">
       <c r="A697" s="2" t="s">
         <v>892</v>
       </c>
@@ -43025,7 +43613,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="698" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:23" ht="30">
       <c r="A698" s="2" t="s">
         <v>893</v>
       </c>
@@ -43082,7 +43670,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="699" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:23" ht="30">
       <c r="A699" s="2" t="s">
         <v>894</v>
       </c>
@@ -43139,7 +43727,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="700" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:23">
       <c r="A700" s="2" t="s">
         <v>896</v>
       </c>
@@ -43196,7 +43784,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="701" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:23">
       <c r="A701" s="2" t="s">
         <v>898</v>
       </c>
@@ -43253,7 +43841,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="702" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:23">
       <c r="A702" s="2" t="s">
         <v>899</v>
       </c>
@@ -43310,7 +43898,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="703" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:23" ht="30">
       <c r="A703" s="2" t="s">
         <v>900</v>
       </c>
@@ -43367,7 +43955,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="704" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:23" ht="30">
       <c r="A704" s="2" t="s">
         <v>901</v>
       </c>
@@ -43424,7 +44012,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="705" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:23" ht="30">
       <c r="A705" s="2" t="s">
         <v>902</v>
       </c>
@@ -43481,7 +44069,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="706" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:23" ht="30">
       <c r="A706" s="2" t="s">
         <v>904</v>
       </c>
@@ -43538,7 +44126,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="707" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:23" ht="30">
       <c r="A707" s="2" t="s">
         <v>905</v>
       </c>
@@ -43595,7 +44183,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="708" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:23" ht="30">
       <c r="A708" s="2" t="s">
         <v>906</v>
       </c>
@@ -43652,7 +44240,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="709" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:23" ht="30">
       <c r="A709" s="2" t="s">
         <v>907</v>
       </c>
@@ -43709,7 +44297,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="710" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:23" ht="30">
       <c r="A710" s="2" t="s">
         <v>909</v>
       </c>
@@ -43766,7 +44354,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="711" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:23">
       <c r="A711" s="2" t="s">
         <v>794</v>
       </c>
@@ -43823,7 +44411,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="712" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:23" ht="30">
       <c r="A712" s="2" t="s">
         <v>911</v>
       </c>
@@ -43880,7 +44468,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="713" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:23" ht="30">
       <c r="A713" s="2" t="s">
         <v>912</v>
       </c>
@@ -43937,7 +44525,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="714" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:23">
       <c r="A714" s="2" t="s">
         <v>914</v>
       </c>
@@ -43994,7 +44582,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="715" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:23">
       <c r="A715" s="2" t="s">
         <v>915</v>
       </c>
@@ -44051,7 +44639,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="716" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:23">
       <c r="A716" s="2" t="s">
         <v>916</v>
       </c>
@@ -44108,7 +44696,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="717" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:23">
       <c r="A717" s="2" t="s">
         <v>917</v>
       </c>
@@ -44165,7 +44753,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="718" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:23">
       <c r="A718" s="2" t="s">
         <v>919</v>
       </c>
@@ -44222,7 +44810,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="719" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:23" ht="30">
       <c r="A719" s="2" t="s">
         <v>921</v>
       </c>
@@ -44279,7 +44867,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="720" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:23" ht="30">
       <c r="A720" s="2" t="s">
         <v>922</v>
       </c>
@@ -44336,7 +44924,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="721" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:23" ht="30">
       <c r="A721" s="2" t="s">
         <v>923</v>
       </c>
@@ -44393,7 +44981,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="722" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:23">
       <c r="A722" s="2" t="s">
         <v>246</v>
       </c>
@@ -44450,7 +45038,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="723" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:23">
       <c r="A723" s="2" t="s">
         <v>246</v>
       </c>
@@ -44515,13 +45103,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{338CFD3C-6782-4E22-A0C1-566C93D94368}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="85" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>935</v>
       </c>
@@ -44529,20 +45122,288 @@
         <v>938</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="6" t="s">
         <v>936</v>
       </c>
       <c r="B2" s="6">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>941</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="6" t="s">
         <v>937</v>
       </c>
       <c r="B3" s="6">
         <v>11</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>945</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="D4" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="D5" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>950</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>951</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="D6" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>952</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>953</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="D7" s="11" t="s">
+        <v>954</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="D8" s="11" t="s">
+        <v>954</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>956</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="D9" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>958</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="D10" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="D11" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>966</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="D13" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="D14" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="D15" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>974</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="D16" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>977</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8">
+      <c r="D17" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>947</v>
       </c>
     </row>
   </sheetData>
